--- a/docs/evidence/phase2/Perhitungan_Manual_Rekomendasi_Hybrid_CBF_ALS.xlsx
+++ b/docs/evidence/phase2/Perhitungan_Manual_Rekomendasi_Hybrid_CBF_ALS.xlsx
@@ -727,7 +727,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>NDCG@5, AP@5, Recall@5 untuk skenario dummy (K diturunkan dari 10 karena hanya ada 9 kandidat)</t>
+          <t>NDCG, AP, MAP, Precision, Recall, F1 pada K - K diturunkan ke 5 karena hanya ada 9 kandidat</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Rata-rata 9 titik evaluasi terkunci vs angka naskah</t>
+          <t>Rata-rata 9 titik evaluasi terkunci untuk enam metrik (NDCG, AP, MAP, Precision, Recall, F1) vs angka naskah</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1750,7 +1750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2202,16 +2202,64 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>MAP@K</t>
+        </is>
+      </c>
+      <c r="B20" s="9">
+        <f>G14/MIN($C$15,'1_Data'!$L$11)</f>
+        <v/>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>sama dengan AP@K pada satu daftar peringkat (alias)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Precision@K</t>
+        </is>
+      </c>
+      <c r="B21" s="9">
+        <f>H14/'1_Data'!$L$11</f>
+        <v/>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>hit dalam K / K</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>Recall@K</t>
         </is>
       </c>
-      <c r="B20" s="9">
+      <c r="B22" s="9">
         <f>H14/$C$15</f>
         <v/>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>hit relevan dalam K / total relevan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>F1@K</t>
+        </is>
+      </c>
+      <c r="B23" s="9">
+        <f>IFERROR(2*(H14/'1_Data'!$L$11)*(H14/$C$15)/((H14/'1_Data'!$L$11)+(H14/$C$15)),0)</f>
+        <v/>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>harmonik Precision@K dan Recall@K (0 bila tak ada hit)</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3240,7 +3288,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Recall@10</t>
+          <t>MAP@10</t>
         </is>
       </c>
     </row>
@@ -3333,31 +3381,31 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>0.006224322054799421</v>
+        <v>0.005443055555555555</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>0.00321408754861257</v>
+        <v>0.002706283068783069</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>0.002258953646213632</v>
+        <v>0.001852910052910053</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>0.005602542426072446</v>
+        <v>0.004679298941798943</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>0.00441988034001324</v>
+        <v>0.003161838624338624</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>0.003938902581097948</v>
+        <v>0.002885251322751323</v>
       </c>
       <c r="H26" s="14" t="n">
-        <v>0.006481969759857614</v>
+        <v>0.004753571428571429</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>0.003265987985425236</v>
+        <v>0.003053042328042329</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>0.002791151871795243</v>
+        <v>0.001393121693121693</v>
       </c>
       <c r="K26" s="15">
         <f>AVERAGE(B26:J26)</f>
@@ -3372,7 +3420,7 @@
         <v/>
       </c>
       <c r="N26" s="14" t="n">
-        <v>0.0042441998</v>
+        <v>0.0033253748</v>
       </c>
       <c r="O26" s="15">
         <f>K26-N26</f>
@@ -3390,31 +3438,31 @@
         </is>
       </c>
       <c r="B27" s="14" t="n">
-        <v>0.0005430124099853451</v>
+        <v>0.0003648148148148148</v>
       </c>
       <c r="C27" s="14" t="n">
-        <v>0.000737951897257113</v>
+        <v>0.0005793320105820106</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>0.0004681503624754039</v>
+        <v>0.0003541666666666667</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>0.0005144756777749105</v>
+        <v>0.0003462301587301587</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>0.0006391595971526401</v>
+        <v>0.0004298280423280423</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>0.0004286315536315536</v>
+        <v>0.0002740740740740741</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>0.0002457441913963653</v>
+        <v>0.0002018518518518519</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>0.0004189763564048461</v>
+        <v>0.0001615740740740741</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>0.0004611841486126384</v>
+        <v>0.000183994708994709</v>
       </c>
       <c r="K27" s="15">
         <f>AVERAGE(B27:J27)</f>
@@ -3429,7 +3477,7 @@
         <v/>
       </c>
       <c r="N27" s="14" t="n">
-        <v>0.000495254</v>
+        <v>0.0003217629</v>
       </c>
       <c r="O27" s="15">
         <f>K27-N27</f>
@@ -3447,31 +3495,31 @@
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>0.00277346566931609</v>
+        <v>0.002574404761904762</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>0.002011696043697034</v>
+        <v>0.001444113756613757</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>0.001948659427766951</v>
+        <v>0.00121468253968254</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>0.003099700670804254</v>
+        <v>0.00207037037037037</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>0.002041520037930537</v>
+        <v>0.001716402116402116</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>0.001692073211550284</v>
+        <v>0.001276058201058201</v>
       </c>
       <c r="H28" s="14" t="n">
-        <v>0.003661108849706704</v>
+        <v>0.002514219576719577</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>0.00202143676045821</v>
+        <v>0.002476587301587302</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>0.001260981868378426</v>
+        <v>0.001351322751322751</v>
       </c>
       <c r="K28" s="15">
         <f>AVERAGE(B28:J28)</f>
@@ -3486,7 +3534,7 @@
         <v/>
       </c>
       <c r="N28" s="14" t="n">
-        <v>0.0022789603</v>
+        <v>0.0018486846</v>
       </c>
       <c r="O28" s="15">
         <f>K28-N28</f>
@@ -3504,31 +3552,31 @@
         </is>
       </c>
       <c r="B29" s="14" t="n">
-        <v>0.001212454800657076</v>
+        <v>0.0008332671957671957</v>
       </c>
       <c r="C29" s="14" t="n">
-        <v>0.001021432669493508</v>
+        <v>0.0007833333333333333</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>0.0008317631989143272</v>
+        <v>0.0003881613756613757</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>0.001069031303781943</v>
+        <v>0.0007837962962962963</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.001280876781486119</v>
+        <v>0.001074007936507937</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0.0007841062350866272</v>
+        <v>0.0004755952380952381</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>0.0006263788264169653</v>
+        <v>0.0003407407407407407</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0.001416523049126209</v>
+        <v>0.0006686507936507936</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>0.000417167479524459</v>
+        <v>0.0002488095238095238</v>
       </c>
       <c r="K29" s="15">
         <f>AVERAGE(B29:J29)</f>
@@ -3543,7 +3591,7 @@
         <v/>
       </c>
       <c r="N29" s="14" t="n">
-        <v>0.0009621927</v>
+        <v>0.000621818</v>
       </c>
       <c r="O29" s="15">
         <f>K29-N29</f>
@@ -3561,31 +3609,31 @@
         </is>
       </c>
       <c r="B30" s="14" t="n">
-        <v>0.001511223663399295</v>
+        <v>0.001130952380952381</v>
       </c>
       <c r="C30" s="14" t="n">
-        <v>0.0009744126305911202</v>
+        <v>0.0005577380952380952</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>0.0009948895354905585</v>
+        <v>0.0004265873015873015</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>0.001290673327925336</v>
+        <v>0.0009383597883597883</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0.001280495101989369</v>
+        <v>0.00124292328042328</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0.0007483140031318</v>
+        <v>0.0004121693121693122</v>
       </c>
       <c r="H30" s="14" t="n">
-        <v>0.000997094026835735</v>
+        <v>0.000418452380952381</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>0.001493483646382579</v>
+        <v>0.0009782407407407409</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>0.0005436718602882762</v>
+        <v>0.0003664021164021165</v>
       </c>
       <c r="K30" s="15">
         <f>AVERAGE(B30:J30)</f>
@@ -3600,7 +3648,7 @@
         <v/>
       </c>
       <c r="N30" s="14" t="n">
-        <v>0.0010926953</v>
+        <v>0.0007190917</v>
       </c>
       <c r="O30" s="15">
         <f>K30-N30</f>
@@ -3618,31 +3666,31 @@
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>0.001632586097261729</v>
+        <v>0.001171693121693122</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>0.001053359999012173</v>
+        <v>0.0005623677248677248</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>0.001139817071722443</v>
+        <v>0.000468452380952381</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>0.001284876226476061</v>
+        <v>0.0009431878306878308</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0.001197161768656036</v>
+        <v>0.001243121693121693</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0.0007483140031318</v>
+        <v>0.0004219576719576719</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>0.001112130258719793</v>
+        <v>0.0005123677248677249</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>0.001631707995133244</v>
+        <v>0.001212698412698413</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>0.0007832200060149116</v>
+        <v>0.000418915343915344</v>
       </c>
       <c r="K31" s="15">
         <f>AVERAGE(B31:J31)</f>
@@ -3657,7 +3705,7 @@
         <v/>
       </c>
       <c r="N31" s="14" t="n">
-        <v>0.0011759082</v>
+        <v>0.0007727513</v>
       </c>
       <c r="O31" s="15">
         <f>K31-N31</f>
@@ -3675,31 +3723,31 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>0.001880839306041254</v>
+        <v>0.00128505291005291</v>
       </c>
       <c r="C32" s="14" t="n">
-        <v>0.001188895759547933</v>
+        <v>0.0006409391534391534</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>0.001189420246325617</v>
+        <v>0.0006166005291005293</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>0.00160505524230725</v>
+        <v>0.001047156084656084</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0.001372156975169372</v>
+        <v>0.001325132275132275</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0.0008217383046262768</v>
+        <v>0.0004640873015873016</v>
       </c>
       <c r="H32" s="14" t="n">
-        <v>0.001369492414108264</v>
+        <v>0.0005240079365079365</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>0.001588482273366743</v>
+        <v>0.00121686507936508</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>0.0008295163023112078</v>
+        <v>0.000354563492063492</v>
       </c>
       <c r="K32" s="15">
         <f>AVERAGE(B32:J32)</f>
@@ -3714,7 +3762,7 @@
         <v/>
       </c>
       <c r="N32" s="14" t="n">
-        <v>0.0013161774</v>
+        <v>0.0008304894</v>
       </c>
       <c r="O32" s="15">
         <f>K32-N32</f>
@@ -3725,8 +3773,1472 @@
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Precision@10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>titik 1</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>titik 2</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>titik 3</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>titik 4</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>titik 5</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>titik 6</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>titik 7</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>titik 8</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>titik 9</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Rata-rata</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Maks</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Dilaporkan</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>Selisih</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Cocok?</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Popularity</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>0.01566666666666667</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>0.008333333333333333</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>0.01266666666666667</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>0.01033333333333333</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>0.009499999999999998</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>0.01483333333333333</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>0.007833333333333333</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>0.006166666666666667</v>
+      </c>
+      <c r="K36" s="15">
+        <f>AVERAGE(B36:J36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="15">
+        <f>MIN(B36:J36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="15">
+        <f>MAX(B36:J36)</f>
+        <v/>
+      </c>
+      <c r="N36" s="14" t="n">
+        <v>0.0100925926</v>
+      </c>
+      <c r="O36" s="15">
+        <f>K36-N36</f>
+        <v/>
+      </c>
+      <c r="P36" s="5">
+        <f>IF(ABS(O36)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>CBF (TF-IDF)</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>0.001666666666666667</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>0.001166666666666667</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>0.001333333333333334</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>0.0008333333333333334</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>0.0006666666666666668</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K37" s="15">
+        <f>AVERAGE(B37:J37)</f>
+        <v/>
+      </c>
+      <c r="L37" s="15">
+        <f>MIN(B37:J37)</f>
+        <v/>
+      </c>
+      <c r="M37" s="15">
+        <f>MAX(B37:J37)</f>
+        <v/>
+      </c>
+      <c r="N37" s="14" t="n">
+        <v>0.0011296296</v>
+      </c>
+      <c r="O37" s="15">
+        <f>K37-N37</f>
+        <v/>
+      </c>
+      <c r="P37" s="5">
+        <f>IF(ABS(O37)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ALS (CF)</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>0.007166666666666668</v>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>0.004333333333333334</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>0.004166666666666667</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>0.007833333333333333</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>0.004833333333333334</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>0.008166666666666668</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>0.004833333333333334</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>0.002833333333333334</v>
+      </c>
+      <c r="K38" s="15">
+        <f>AVERAGE(B38:J38)</f>
+        <v/>
+      </c>
+      <c r="L38" s="15">
+        <f>MIN(B38:J38)</f>
+        <v/>
+      </c>
+      <c r="M38" s="15">
+        <f>MAX(B38:J38)</f>
+        <v/>
+      </c>
+      <c r="N38" s="14" t="n">
+        <v>0.0052962963</v>
+      </c>
+      <c r="O38" s="15">
+        <f>K38-N38</f>
+        <v/>
+      </c>
+      <c r="P38" s="5">
+        <f>IF(ABS(O38)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid alpha 0,2</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>0.003333333333333334</v>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>0.002333333333333334</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>0.001833333333333334</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>0.002333333333333334</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>0.003166666666666667</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>0.001666666666666667</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K39" s="15">
+        <f>AVERAGE(B39:J39)</f>
+        <v/>
+      </c>
+      <c r="L39" s="15">
+        <f>MIN(B39:J39)</f>
+        <v/>
+      </c>
+      <c r="M39" s="15">
+        <f>MAX(B39:J39)</f>
+        <v/>
+      </c>
+      <c r="N39" s="14" t="n">
+        <v>0.0022407407</v>
+      </c>
+      <c r="O39" s="15">
+        <f>K39-N39</f>
+        <v/>
+      </c>
+      <c r="P39" s="5">
+        <f>IF(ABS(O39)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid alpha 0,4</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>0.004333333333333333</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>0.002333333333333333</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>0.002166666666666667</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>0.003166666666666667</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>0.003500000000000001</v>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>0.001833333333333334</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>0.002166666666666667</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>0.003166666666666667</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>0.001333333333333334</v>
+      </c>
+      <c r="K40" s="15">
+        <f>AVERAGE(B40:J40)</f>
+        <v/>
+      </c>
+      <c r="L40" s="15">
+        <f>MIN(B40:J40)</f>
+        <v/>
+      </c>
+      <c r="M40" s="15">
+        <f>MAX(B40:J40)</f>
+        <v/>
+      </c>
+      <c r="N40" s="14" t="n">
+        <v>0.0026666667</v>
+      </c>
+      <c r="O40" s="15">
+        <f>K40-N40</f>
+        <v/>
+      </c>
+      <c r="P40" s="5">
+        <f>IF(ABS(O40)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid alpha 0,6</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>0.004500000000000001</v>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>0.003166666666666667</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>0.003333333333333334</v>
+      </c>
+      <c r="G41" s="14" t="n">
+        <v>0.001833333333333334</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>0.002333333333333333</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="J41" s="14" t="n">
+        <v>0.001833333333333334</v>
+      </c>
+      <c r="K41" s="15">
+        <f>AVERAGE(B41:J41)</f>
+        <v/>
+      </c>
+      <c r="L41" s="15">
+        <f>MIN(B41:J41)</f>
+        <v/>
+      </c>
+      <c r="M41" s="15">
+        <f>MAX(B41:J41)</f>
+        <v/>
+      </c>
+      <c r="N41" s="14" t="n">
+        <v>0.0028333333</v>
+      </c>
+      <c r="O41" s="15">
+        <f>K41-N41</f>
+        <v/>
+      </c>
+      <c r="P41" s="5">
+        <f>IF(ABS(O41)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid alpha 0,8 (dilayani)</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>0.005166666666666667</v>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>0.002666666666666667</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>0.002666666666666667</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>0.003833333333333334</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>0.003833333333333334</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>0.002666666666666667</v>
+      </c>
+      <c r="I42" s="14" t="n">
+        <v>0.003333333333333334</v>
+      </c>
+      <c r="J42" s="14" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K42" s="15">
+        <f>AVERAGE(B42:J42)</f>
+        <v/>
+      </c>
+      <c r="L42" s="15">
+        <f>MIN(B42:J42)</f>
+        <v/>
+      </c>
+      <c r="M42" s="15">
+        <f>MAX(B42:J42)</f>
+        <v/>
+      </c>
+      <c r="N42" s="14" t="n">
+        <v>0.0031296296</v>
+      </c>
+      <c r="O42" s="15">
+        <f>K42-N42</f>
+        <v/>
+      </c>
+      <c r="P42" s="5">
+        <f>IF(ABS(O42)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>Recall@10</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>titik 1</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>titik 2</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>titik 3</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>titik 4</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>titik 5</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>titik 6</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>titik 7</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>titik 8</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>titik 9</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Rata-rata</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Maks</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Dilaporkan</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>Selisih</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Cocok?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Popularity</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>0.006224322054799421</v>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>0.00321408754861257</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>0.002258953646213632</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>0.005602542426072446</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>0.00441988034001324</v>
+      </c>
+      <c r="G46" s="14" t="n">
+        <v>0.003938902581097948</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>0.006481969759857614</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <v>0.003265987985425236</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>0.002791151871795243</v>
+      </c>
+      <c r="K46" s="15">
+        <f>AVERAGE(B46:J46)</f>
+        <v/>
+      </c>
+      <c r="L46" s="15">
+        <f>MIN(B46:J46)</f>
+        <v/>
+      </c>
+      <c r="M46" s="15">
+        <f>MAX(B46:J46)</f>
+        <v/>
+      </c>
+      <c r="N46" s="14" t="n">
+        <v>0.0042441998</v>
+      </c>
+      <c r="O46" s="15">
+        <f>K46-N46</f>
+        <v/>
+      </c>
+      <c r="P46" s="5">
+        <f>IF(ABS(O46)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>CBF (TF-IDF)</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="n">
+        <v>0.0005430124099853451</v>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>0.000737951897257113</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>0.0004681503624754039</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>0.0005144756777749105</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>0.0006391595971526401</v>
+      </c>
+      <c r="G47" s="14" t="n">
+        <v>0.0004286315536315536</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>0.0002457441913963653</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>0.0004189763564048461</v>
+      </c>
+      <c r="J47" s="14" t="n">
+        <v>0.0004611841486126384</v>
+      </c>
+      <c r="K47" s="15">
+        <f>AVERAGE(B47:J47)</f>
+        <v/>
+      </c>
+      <c r="L47" s="15">
+        <f>MIN(B47:J47)</f>
+        <v/>
+      </c>
+      <c r="M47" s="15">
+        <f>MAX(B47:J47)</f>
+        <v/>
+      </c>
+      <c r="N47" s="14" t="n">
+        <v>0.000495254</v>
+      </c>
+      <c r="O47" s="15">
+        <f>K47-N47</f>
+        <v/>
+      </c>
+      <c r="P47" s="5">
+        <f>IF(ABS(O47)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ALS (CF)</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n">
+        <v>0.00277346566931609</v>
+      </c>
+      <c r="C48" s="14" t="n">
+        <v>0.002011696043697034</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>0.001948659427766951</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>0.003099700670804254</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>0.002041520037930537</v>
+      </c>
+      <c r="G48" s="14" t="n">
+        <v>0.001692073211550284</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>0.003661108849706704</v>
+      </c>
+      <c r="I48" s="14" t="n">
+        <v>0.00202143676045821</v>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>0.001260981868378426</v>
+      </c>
+      <c r="K48" s="15">
+        <f>AVERAGE(B48:J48)</f>
+        <v/>
+      </c>
+      <c r="L48" s="15">
+        <f>MIN(B48:J48)</f>
+        <v/>
+      </c>
+      <c r="M48" s="15">
+        <f>MAX(B48:J48)</f>
+        <v/>
+      </c>
+      <c r="N48" s="14" t="n">
+        <v>0.0022789603</v>
+      </c>
+      <c r="O48" s="15">
+        <f>K48-N48</f>
+        <v/>
+      </c>
+      <c r="P48" s="5">
+        <f>IF(ABS(O48)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid alpha 0,2</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n">
+        <v>0.001212454800657076</v>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>0.001021432669493508</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>0.0008317631989143272</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>0.001069031303781943</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>0.001280876781486119</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>0.0007841062350866272</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>0.0006263788264169653</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>0.001416523049126209</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>0.000417167479524459</v>
+      </c>
+      <c r="K49" s="15">
+        <f>AVERAGE(B49:J49)</f>
+        <v/>
+      </c>
+      <c r="L49" s="15">
+        <f>MIN(B49:J49)</f>
+        <v/>
+      </c>
+      <c r="M49" s="15">
+        <f>MAX(B49:J49)</f>
+        <v/>
+      </c>
+      <c r="N49" s="14" t="n">
+        <v>0.0009621927</v>
+      </c>
+      <c r="O49" s="15">
+        <f>K49-N49</f>
+        <v/>
+      </c>
+      <c r="P49" s="5">
+        <f>IF(ABS(O49)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid alpha 0,4</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>0.001511223663399295</v>
+      </c>
+      <c r="C50" s="14" t="n">
+        <v>0.0009744126305911202</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>0.0009948895354905585</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>0.001290673327925336</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>0.001280495101989369</v>
+      </c>
+      <c r="G50" s="14" t="n">
+        <v>0.0007483140031318</v>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>0.000997094026835735</v>
+      </c>
+      <c r="I50" s="14" t="n">
+        <v>0.001493483646382579</v>
+      </c>
+      <c r="J50" s="14" t="n">
+        <v>0.0005436718602882762</v>
+      </c>
+      <c r="K50" s="15">
+        <f>AVERAGE(B50:J50)</f>
+        <v/>
+      </c>
+      <c r="L50" s="15">
+        <f>MIN(B50:J50)</f>
+        <v/>
+      </c>
+      <c r="M50" s="15">
+        <f>MAX(B50:J50)</f>
+        <v/>
+      </c>
+      <c r="N50" s="14" t="n">
+        <v>0.0010926953</v>
+      </c>
+      <c r="O50" s="15">
+        <f>K50-N50</f>
+        <v/>
+      </c>
+      <c r="P50" s="5">
+        <f>IF(ABS(O50)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid alpha 0,6</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="n">
+        <v>0.001632586097261729</v>
+      </c>
+      <c r="C51" s="14" t="n">
+        <v>0.001053359999012173</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>0.001139817071722443</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>0.001284876226476061</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>0.001197161768656036</v>
+      </c>
+      <c r="G51" s="14" t="n">
+        <v>0.0007483140031318</v>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>0.001112130258719793</v>
+      </c>
+      <c r="I51" s="14" t="n">
+        <v>0.001631707995133244</v>
+      </c>
+      <c r="J51" s="14" t="n">
+        <v>0.0007832200060149116</v>
+      </c>
+      <c r="K51" s="15">
+        <f>AVERAGE(B51:J51)</f>
+        <v/>
+      </c>
+      <c r="L51" s="15">
+        <f>MIN(B51:J51)</f>
+        <v/>
+      </c>
+      <c r="M51" s="15">
+        <f>MAX(B51:J51)</f>
+        <v/>
+      </c>
+      <c r="N51" s="14" t="n">
+        <v>0.0011759082</v>
+      </c>
+      <c r="O51" s="15">
+        <f>K51-N51</f>
+        <v/>
+      </c>
+      <c r="P51" s="5">
+        <f>IF(ABS(O51)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid alpha 0,8 (dilayani)</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="n">
+        <v>0.001880839306041254</v>
+      </c>
+      <c r="C52" s="14" t="n">
+        <v>0.001188895759547933</v>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>0.001189420246325617</v>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>0.00160505524230725</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>0.001372156975169372</v>
+      </c>
+      <c r="G52" s="14" t="n">
+        <v>0.0008217383046262768</v>
+      </c>
+      <c r="H52" s="14" t="n">
+        <v>0.001369492414108264</v>
+      </c>
+      <c r="I52" s="14" t="n">
+        <v>0.001588482273366743</v>
+      </c>
+      <c r="J52" s="14" t="n">
+        <v>0.0008295163023112078</v>
+      </c>
+      <c r="K52" s="15">
+        <f>AVERAGE(B52:J52)</f>
+        <v/>
+      </c>
+      <c r="L52" s="15">
+        <f>MIN(B52:J52)</f>
+        <v/>
+      </c>
+      <c r="M52" s="15">
+        <f>MAX(B52:J52)</f>
+        <v/>
+      </c>
+      <c r="N52" s="14" t="n">
+        <v>0.0013161774</v>
+      </c>
+      <c r="O52" s="15">
+        <f>K52-N52</f>
+        <v/>
+      </c>
+      <c r="P52" s="5">
+        <f>IF(ABS(O52)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>F1@10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>titik 1</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>titik 2</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>titik 3</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>titik 4</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>titik 5</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>titik 6</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>titik 7</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>titik 8</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>titik 9</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Rata-rata</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Maks</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Dilaporkan</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>Selisih</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>Cocok?</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Popularity</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="n">
+        <v>0.008706259759838337</v>
+      </c>
+      <c r="C56" s="14" t="n">
+        <v>0.004541224023537669</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>0.003122083174097016</v>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>0.00751029896692217</v>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>0.006053899985597397</v>
+      </c>
+      <c r="G56" s="14" t="n">
+        <v>0.005438855775014126</v>
+      </c>
+      <c r="H56" s="14" t="n">
+        <v>0.008793504912166903</v>
+      </c>
+      <c r="I56" s="14" t="n">
+        <v>0.004510753814933256</v>
+      </c>
+      <c r="J56" s="14" t="n">
+        <v>0.003759541140045607</v>
+      </c>
+      <c r="K56" s="15">
+        <f>AVERAGE(B56:J56)</f>
+        <v/>
+      </c>
+      <c r="L56" s="15">
+        <f>MIN(B56:J56)</f>
+        <v/>
+      </c>
+      <c r="M56" s="15">
+        <f>MAX(B56:J56)</f>
+        <v/>
+      </c>
+      <c r="N56" s="14" t="n">
+        <v>0.0058262691</v>
+      </c>
+      <c r="O56" s="15">
+        <f>K56-N56</f>
+        <v/>
+      </c>
+      <c r="P56" s="5">
+        <f>IF(ABS(O56)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>CBF (TF-IDF)</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="n">
+        <v>0.0007835281693408231</v>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>0.0009582717841103331</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>0.0006200222443416636</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>0.000708454951640748</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>0.0008396180169435983</v>
+      </c>
+      <c r="G57" s="14" t="n">
+        <v>0.0005432748538011697</v>
+      </c>
+      <c r="H57" s="14" t="n">
+        <v>0.0003550748249205472</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>0.0005846695609626643</v>
+      </c>
+      <c r="J57" s="14" t="n">
+        <v>0.0006192528595650928</v>
+      </c>
+      <c r="K57" s="15">
+        <f>AVERAGE(B57:J57)</f>
+        <v/>
+      </c>
+      <c r="L57" s="15">
+        <f>MIN(B57:J57)</f>
+        <v/>
+      </c>
+      <c r="M57" s="15">
+        <f>MAX(B57:J57)</f>
+        <v/>
+      </c>
+      <c r="N57" s="14" t="n">
+        <v>0.0006680186</v>
+      </c>
+      <c r="O57" s="15">
+        <f>K57-N57</f>
+        <v/>
+      </c>
+      <c r="P57" s="5">
+        <f>IF(ABS(O57)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>ALS (CF)</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="n">
+        <v>0.003885269215273189</v>
+      </c>
+      <c r="C58" s="14" t="n">
+        <v>0.002658738801766692</v>
+      </c>
+      <c r="D58" s="14" t="n">
+        <v>0.002553140777566646</v>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>0.004355065685579849</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>0.00281053295150517</v>
+      </c>
+      <c r="G58" s="14" t="n">
+        <v>0.002207241951788266</v>
+      </c>
+      <c r="H58" s="14" t="n">
+        <v>0.004936433918228817</v>
+      </c>
+      <c r="I58" s="14" t="n">
+        <v>0.002791434730050208</v>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>0.001691971479188976</v>
+      </c>
+      <c r="K58" s="15">
+        <f>AVERAGE(B58:J58)</f>
+        <v/>
+      </c>
+      <c r="L58" s="15">
+        <f>MIN(B58:J58)</f>
+        <v/>
+      </c>
+      <c r="M58" s="15">
+        <f>MAX(B58:J58)</f>
+        <v/>
+      </c>
+      <c r="N58" s="14" t="n">
+        <v>0.0030988699</v>
+      </c>
+      <c r="O58" s="15">
+        <f>K58-N58</f>
+        <v/>
+      </c>
+      <c r="P58" s="5">
+        <f>IF(ABS(O58)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid alpha 0,2</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="n">
+        <v>0.001740215475382505</v>
+      </c>
+      <c r="C59" s="14" t="n">
+        <v>0.001337097219133733</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>0.001110918602885081</v>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>0.001450166172518636</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>0.001775971012547909</v>
+      </c>
+      <c r="G59" s="14" t="n">
+        <v>0.001039157329649545</v>
+      </c>
+      <c r="H59" s="14" t="n">
+        <v>0.0008751694467949245</v>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>0.00188517343108606</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>0.0005818884074523696</v>
+      </c>
+      <c r="K59" s="15">
+        <f>AVERAGE(B59:J59)</f>
+        <v/>
+      </c>
+      <c r="L59" s="15">
+        <f>MIN(B59:J59)</f>
+        <v/>
+      </c>
+      <c r="M59" s="15">
+        <f>MAX(B59:J59)</f>
+        <v/>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v>0.0013106397</v>
+      </c>
+      <c r="O59" s="15">
+        <f>K59-N59</f>
+        <v/>
+      </c>
+      <c r="P59" s="5">
+        <f>IF(ABS(O59)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid alpha 0,4</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="n">
+        <v>0.002203001509300194</v>
+      </c>
+      <c r="C60" s="14" t="n">
+        <v>0.001346213358686351</v>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>0.001328299959275175</v>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>0.0018015776546895</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>0.001844031485612046</v>
+      </c>
+      <c r="G60" s="14" t="n">
+        <v>0.001042847491118905</v>
+      </c>
+      <c r="H60" s="14" t="n">
+        <v>0.001348508510688711</v>
+      </c>
+      <c r="I60" s="14" t="n">
+        <v>0.001986539436306021</v>
+      </c>
+      <c r="J60" s="14" t="n">
+        <v>0.0007594431499501204</v>
+      </c>
+      <c r="K60" s="15">
+        <f>AVERAGE(B60:J60)</f>
+        <v/>
+      </c>
+      <c r="L60" s="15">
+        <f>MIN(B60:J60)</f>
+        <v/>
+      </c>
+      <c r="M60" s="15">
+        <f>MAX(B60:J60)</f>
+        <v/>
+      </c>
+      <c r="N60" s="14" t="n">
+        <v>0.0015178292</v>
+      </c>
+      <c r="O60" s="15">
+        <f>K60-N60</f>
+        <v/>
+      </c>
+      <c r="P60" s="5">
+        <f>IF(ABS(O60)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid alpha 0,6</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="n">
+        <v>0.002347113339744791</v>
+      </c>
+      <c r="C61" s="14" t="n">
+        <v>0.001447937496617386</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>0.001530320161295378</v>
+      </c>
+      <c r="E61" s="14" t="n">
+        <v>0.001795805648917495</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>0.001732920374500935</v>
+      </c>
+      <c r="G61" s="14" t="n">
+        <v>0.001042847491118905</v>
+      </c>
+      <c r="H61" s="14" t="n">
+        <v>0.001486814648994849</v>
+      </c>
+      <c r="I61" s="14" t="n">
+        <v>0.002179001344886614</v>
+      </c>
+      <c r="J61" s="14" t="n">
+        <v>0.001082922661416284</v>
+      </c>
+      <c r="K61" s="15">
+        <f>AVERAGE(B61:J61)</f>
+        <v/>
+      </c>
+      <c r="L61" s="15">
+        <f>MIN(B61:J61)</f>
+        <v/>
+      </c>
+      <c r="M61" s="15">
+        <f>MAX(B61:J61)</f>
+        <v/>
+      </c>
+      <c r="N61" s="14" t="n">
+        <v>0.0016272981</v>
+      </c>
+      <c r="O61" s="15">
+        <f>K61-N61</f>
+        <v/>
+      </c>
+      <c r="P61" s="5">
+        <f>IF(ABS(O61)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid alpha 0,8 (dilayani)</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>0.00270481392641596</v>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>0.001612612237481473</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>0.001607719542100331</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>0.002227556917362311</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>0.001987381360669238</v>
+      </c>
+      <c r="G62" s="14" t="n">
+        <v>0.001146826470097884</v>
+      </c>
+      <c r="H62" s="14" t="n">
+        <v>0.001782594082760935</v>
+      </c>
+      <c r="I62" s="14" t="n">
+        <v>0.002103757399978116</v>
+      </c>
+      <c r="J62" s="14" t="n">
+        <v>0.001155386429532226</v>
+      </c>
+      <c r="K62" s="15">
+        <f>AVERAGE(B62:J62)</f>
+        <v/>
+      </c>
+      <c r="L62" s="15">
+        <f>MIN(B62:J62)</f>
+        <v/>
+      </c>
+      <c r="M62" s="15">
+        <f>MAX(B62:J62)</f>
+        <v/>
+      </c>
+      <c r="N62" s="14" t="n">
+        <v>0.0018142943</v>
+      </c>
+      <c r="O62" s="15">
+        <f>K62-N62</f>
+        <v/>
+      </c>
+      <c r="P62" s="5">
+        <f>IF(ABS(O62)&lt;0.0000005,"cocok","periksa")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>Catatan: alpha pemenang = 0,8 (rata-rata NDCG@10 tertinggi pada grid 0,2-0,8). Angka inilah yang dilayani web. Workbook ini tidak mengubah satu pun nilai terkunci.</t>
         </is>
